--- a/results/emp008_runs/origin_emp008/factor_attribution/factor_attribution.xlsx
+++ b/results/emp008_runs/origin_emp008/factor_attribution/factor_attribution.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH41"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4765,6 +4765,110 @@
       </c>
       <c r="AH41" t="n">
         <v>0.002704383051600417</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1.885202576863951e-05</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.004377208646655722</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6.727246036862064e-05</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-5.952562943160773e-19</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-4.29649180923056e-19</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-1.619045738796289e-20</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-3.457941425738121e-19</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.178520275941182e-20</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.523216212911721e-18</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.276975551088366e-18</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.525520172317179e-19</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-2.065575659569452e-21</v>
+      </c>
+      <c r="N42" t="n">
+        <v>7.719801181858446e-20</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-2.014997466839825e-20</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-2.120828361549748e-19</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-5.893609303806764e-19</v>
+      </c>
+      <c r="R42" t="n">
+        <v>9.196599769553691e-19</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-1.468729868160989e-19</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-1.192931466233781e-19</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.212740525778999e-19</v>
+      </c>
+      <c r="V42" t="n">
+        <v>4.702133673364525e-19</v>
+      </c>
+      <c r="W42" t="n">
+        <v>8.619508864666437e-19</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-3.694957421958223e-19</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-4.256840424892674e-18</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>8.887712560137948e-19</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-1.245102509462345e-21</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>3.265278859166337e-21</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-5.584927628869092e-20</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-5.16513104209673e-19</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.004463333132792982</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>9.020263841880093e-20</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.002089402105838164</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.006552735238631147</v>
       </c>
     </row>
   </sheetData>
@@ -4778,7 +4882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5606,6 +5710,26 @@
       </c>
       <c r="F41" t="n">
         <v>-0.005963685741596229</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.00491938133350129</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.01697842087584621</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-0.001921385025850917</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-2.217685944437445e-16</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.003874283635758064</v>
       </c>
     </row>
   </sheetData>
@@ -5714,19 +5838,19 @@
         <v>2026</v>
       </c>
       <c r="B5" t="n">
-        <v>-9.27410872863266e-05</v>
+        <v>-7.38890615176871e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008232893506648627</v>
+        <v>0.01261010215330435</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0004845528954535238</v>
+        <v>-0.0004172804350849032</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.052255243300107e-16</v>
+        <v>-1.051353216915919e-16</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004537189147129854</v>
+        <v>0.006626591252968017</v>
       </c>
     </row>
   </sheetData>
@@ -5777,10 +5901,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49.00529307732652</v>
+        <v>49.19381333501291</v>
       </c>
       <c r="C2" t="n">
-        <v>1.225132326933163</v>
+        <v>1.199849105732022</v>
       </c>
       <c r="D2" t="n">
         <v>34.05038515230126</v>
@@ -5789,7 +5913,7 @@
         <v>-20.60168032462118</v>
       </c>
       <c r="F2" t="n">
-        <v>47.5</v>
+        <v>48.78048780487805</v>
       </c>
     </row>
     <row r="3">
@@ -5799,10 +5923,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126.0121222919049</v>
+        <v>169.7842087584621</v>
       </c>
       <c r="C3" t="n">
-        <v>3.150303057297621</v>
+        <v>4.141078262401514</v>
       </c>
       <c r="D3" t="n">
         <v>53.67939207146565</v>
@@ -5811,7 +5935,7 @@
         <v>-30.69988694764706</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>46.34146341463415</v>
       </c>
     </row>
     <row r="4">
@@ -5821,10 +5945,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-19.88657486219538</v>
+        <v>-19.21385025850918</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.4971643715548845</v>
+        <v>-0.4686304941099799</v>
       </c>
       <c r="D4" t="n">
         <v>18.24648948944337</v>
@@ -5833,7 +5957,7 @@
         <v>-22.93231937531112</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>46.34146341463415</v>
       </c>
     </row>
     <row r="5">
@@ -5843,10 +5967,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.218587970821632e-12</v>
+        <v>-2.217685944437444e-12</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.54646992705408e-14</v>
+        <v>-5.408990108384011e-14</v>
       </c>
       <c r="D5" t="n">
         <v>1.357412484078607e-12</v>
@@ -5855,7 +5979,7 @@
         <v>-1.687204206477238e-12</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>46.34146341463415</v>
       </c>
     </row>
     <row r="6">
@@ -5865,10 +5989,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-59.63685741596229</v>
+        <v>-38.74283635758064</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.490921435399057</v>
+        <v>-0.9449472282336743</v>
       </c>
       <c r="D6" t="n">
         <v>48.73283160347585</v>
@@ -5877,7 +6001,7 @@
         <v>-38.23966123677798</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>46.34146341463415</v>
       </c>
     </row>
   </sheetData>
@@ -5891,7 +6015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD41"/>
+  <dimension ref="A1:AD42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9719,6 +9843,98 @@
       </c>
       <c r="AD41" t="n">
         <v>1.884023620842218e-17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0004243216430854673</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.06246907632094321</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.002916746011385158</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.474719848811872e-18</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7.263307522705625e-18</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.090053797349986e-19</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.144263905974261e-18</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-6.517918529121841e-19</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-1.264789596840121e-17</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-6.349358972618235e-18</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-4.021712433563418e-18</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.981555974335137e-19</v>
+      </c>
+      <c r="N42" t="n">
+        <v>5.844527336054672e-19</v>
+      </c>
+      <c r="O42" t="n">
+        <v>8.487270131488089e-19</v>
+      </c>
+      <c r="P42" t="n">
+        <v>7.599420784087972e-18</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7.267225050086677e-18</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.074916573801229e-17</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-8.039613218864192e-18</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-2.764715539838036e-18</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-1.983751162469571e-18</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-4.352902315939849e-18</v>
+      </c>
+      <c r="W42" t="n">
+        <v>7.788467950003292e-18</v>
+      </c>
+      <c r="X42" t="n">
+        <v>-3.337309812181943e-18</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-1.05777474453117e-17</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.954450920023e-18</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-3.599890025830776e-19</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>8.84090638696676e-21</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.435720845596039e-19</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>4.018112543537587e-18</v>
       </c>
     </row>
   </sheetData>
@@ -9732,7 +9948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD41"/>
+  <dimension ref="A1:AD42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13560,6 +13776,98 @@
       </c>
       <c r="AD41" t="n">
         <v>-0.05069735881609454</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B42" t="n">
+        <v>0.04442862172091166</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.07007000750526912</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.02306421611824649</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.09632053087292464</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.06191897251536364</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.08533177824915755</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.1518756202439749</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.1655254079477773</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.2057243037446062</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-0.1771130915737692</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.08557153729662553</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-0.005862022393378692</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.1238306058275333</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-0.01548755940831971</v>
+      </c>
+      <c r="P42" t="n">
+        <v>-0.02794455572126639</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>-0.08732361646406177</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.08398382291945207</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.01759304155284346</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.04584521136477009</v>
+      </c>
+      <c r="U42" t="n">
+        <v>-0.1481615056357006</v>
+      </c>
+      <c r="V42" t="n">
+        <v>-0.1045048873167797</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.1115802625035597</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.1175171274588224</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.408983572294876</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.5123417468673708</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-0.003828014556264234</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.2409350537773429</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-0.1030237306399377</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>-0.1370933099866634</v>
       </c>
     </row>
   </sheetData>
@@ -13573,7 +13881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14363,6 +14671,25 @@
         <v>1.682681771697503e-16</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.006552735238631153</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.006552735238631147</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.071532165918825e-18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
